--- a/SGC-CKN/Excel/dbd017ad-7cf6-495c-b512-0f1ca449a9e6_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-15_D800_16-03-2026.xlsx
+++ b/SGC-CKN/Excel/dbd017ad-7cf6-495c-b512-0f1ca449a9e6_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-15_D800_16-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P11-15</t>
+    <t>P11-115</t>
   </si>
   <si>
     <t>Biên bản số</t>
@@ -227,7 +227,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -305,6 +305,12 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
       <name val="Arial"/>
     </font>
@@ -315,7 +321,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -390,6 +396,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFBCFE8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -485,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -586,13 +597,16 @@
     <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1213,10 +1227,10 @@
         <v>32</v>
       </c>
       <c r="F12" s="9">
-        <v>0</v>
+        <v>-1.45</v>
       </c>
       <c r="G12" s="9">
-        <v>-1.6</v>
+        <v>-3.05</v>
       </c>
       <c r="H12" s="9">
         <v>0.17</v>
@@ -1248,10 +1262,10 @@
         <v>35</v>
       </c>
       <c r="F13" s="13">
-        <v>0</v>
+        <v>-3.05</v>
       </c>
       <c r="G13" s="13">
-        <v>-10.2</v>
+        <v>-13.25</v>
       </c>
       <c r="H13" s="13">
         <v>0.25</v>
@@ -1283,10 +1297,10 @@
         <v>38</v>
       </c>
       <c r="F14" s="16">
-        <v>0</v>
+        <v>-13.25</v>
       </c>
       <c r="G14" s="16">
-        <v>-5.2</v>
+        <v>-18.45</v>
       </c>
       <c r="H14" s="16">
         <v>0.25</v>
@@ -1318,10 +1332,10 @@
         <v>41</v>
       </c>
       <c r="F15" s="19">
-        <v>0</v>
+        <v>-18.45</v>
       </c>
       <c r="G15" s="19">
-        <v>-10.07</v>
+        <v>-28.52</v>
       </c>
       <c r="H15" s="19">
         <v>0.58</v>
@@ -1353,10 +1367,10 @@
         <v>44</v>
       </c>
       <c r="F16" s="22">
-        <v>0</v>
+        <v>-28.52</v>
       </c>
       <c r="G16" s="22">
-        <v>-6.8</v>
+        <v>-35.32</v>
       </c>
       <c r="H16" s="22">
         <v>0.5</v>
@@ -1388,10 +1402,10 @@
         <v>47</v>
       </c>
       <c r="F17" s="25">
-        <v>0</v>
+        <v>-35.32</v>
       </c>
       <c r="G17" s="25">
-        <v>-2.5</v>
+        <v>-37.82</v>
       </c>
       <c r="H17" s="25">
         <v>1.77</v>
@@ -1423,10 +1437,10 @@
         <v>50</v>
       </c>
       <c r="F18" s="28">
-        <v>0</v>
+        <v>-37.82</v>
       </c>
       <c r="G18" s="28">
-        <v>-6</v>
+        <v>-43.82</v>
       </c>
       <c r="H18" s="28">
         <v>4.23</v>
@@ -1458,38 +1472,38 @@
         <v>54</v>
       </c>
       <c r="F19" s="31">
-        <v>0</v>
+        <v>-43.82</v>
       </c>
       <c r="G19" s="31">
-        <v>-6.1</v>
+        <v>-44</v>
       </c>
       <c r="H19" s="31">
         <v>2.12</v>
       </c>
       <c r="I19" s="31">
-        <v>6.1</v>
-      </c>
-      <c r="J19" s="8">
-        <v>2.88</v>
+        <v>0.18</v>
+      </c>
+      <c r="J19" s="34">
+        <v>0.09</v>
       </c>
       <c r="K19" s="32" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="34" t="s">
+      <c r="A22" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="34"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="34"/>
-      <c r="K22" s="34"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
     </row>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1654,10 +1668,10 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>0</v>
+        <v>-1.45</v>
       </c>
       <c r="F3" s="9">
-        <v>-1.6</v>
+        <v>-3.05</v>
       </c>
       <c r="G3" s="9">
         <v>0.17</v>
@@ -1683,10 +1697,10 @@
         <v>1</v>
       </c>
       <c r="E4" s="13">
-        <v>0</v>
+        <v>-3.05</v>
       </c>
       <c r="F4" s="13">
-        <v>-10.2</v>
+        <v>-13.25</v>
       </c>
       <c r="G4" s="13">
         <v>0.25</v>
@@ -1712,10 +1726,10 @@
         <v>1</v>
       </c>
       <c r="E5" s="16">
-        <v>0</v>
+        <v>-13.25</v>
       </c>
       <c r="F5" s="16">
-        <v>-5.2</v>
+        <v>-18.45</v>
       </c>
       <c r="G5" s="16">
         <v>0.25</v>
@@ -1741,10 +1755,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="19">
-        <v>0</v>
+        <v>-18.45</v>
       </c>
       <c r="F6" s="19">
-        <v>-10.07</v>
+        <v>-28.52</v>
       </c>
       <c r="G6" s="19">
         <v>0.58</v>
@@ -1770,10 +1784,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="22">
-        <v>0</v>
+        <v>-28.52</v>
       </c>
       <c r="F7" s="22">
-        <v>-6.8</v>
+        <v>-35.32</v>
       </c>
       <c r="G7" s="22">
         <v>0.5</v>
@@ -1799,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>0</v>
+        <v>-35.32</v>
       </c>
       <c r="F8" s="25">
-        <v>-2.5</v>
+        <v>-37.82</v>
       </c>
       <c r="G8" s="25">
         <v>1.77</v>
@@ -1828,10 +1842,10 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>0</v>
+        <v>-37.82</v>
       </c>
       <c r="F9" s="28">
-        <v>-6</v>
+        <v>-43.82</v>
       </c>
       <c r="G9" s="28">
         <v>4.23</v>
@@ -1857,48 +1871,48 @@
         <v>1</v>
       </c>
       <c r="E10" s="31">
-        <v>0</v>
+        <v>-43.82</v>
       </c>
       <c r="F10" s="31">
-        <v>-6.1</v>
+        <v>-44</v>
       </c>
       <c r="G10" s="31">
         <v>2.12</v>
       </c>
       <c r="H10" s="31">
-        <v>6.1</v>
-      </c>
-      <c r="I10" s="8">
-        <v>2.88</v>
+        <v>0.18</v>
+      </c>
+      <c r="I10" s="34">
+        <v>0.09</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="B11" s="36" t="s">
+      <c r="B11" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="36">
+      <c r="D11" s="37">
         <v>9</v>
       </c>
-      <c r="E11" s="36">
+      <c r="E11" s="37">
         <v>0</v>
       </c>
-      <c r="F11" s="36">
-        <v>-6.1</v>
-      </c>
-      <c r="G11" s="36">
+      <c r="F11" s="37">
+        <v>-44</v>
+      </c>
+      <c r="G11" s="37">
         <v>10.2</v>
       </c>
-      <c r="H11" s="36">
-        <v>49.92</v>
-      </c>
-      <c r="I11" s="36">
-        <v>4.89</v>
+      <c r="H11" s="37">
+        <v>44</v>
+      </c>
+      <c r="I11" s="37">
+        <v>4.31</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/dbd017ad-7cf6-495c-b512-0f1ca449a9e6_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-15_D800_16-03-2026.xlsx
+++ b/SGC-CKN/Excel/dbd017ad-7cf6-495c-b512-0f1ca449a9e6_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-15_D800_16-03-2026.xlsx
@@ -17,7 +17,7 @@
     <t>Dự án</t>
   </si>
   <si>
-    <t>Dự án số 1 khu đô thị trung tâm thành phố Thanh Hóa (Vinhomes Star City)</t>
+    <t>Star City Thanh Hóa</t>
   </si>
   <si>
     <t>Hạng mục</t>
@@ -38,10 +38,10 @@
     <t>P11-115</t>
   </si>
   <si>
-    <t>Biên bản số</t>
-  </si>
-  <si>
-    <t/>
+    <t>Tên Máy khoan</t>
+  </si>
+  <si>
+    <t>SGC-KCN0003</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Đất Lấp</t>
+    <t>Đất san lấp / Cát san lấp</t>
   </si>
   <si>
     <t xml:space="preserve">23h55
@@ -106,10 +106,13 @@
 16/03/2026</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>Sét pha, xám nâu, TT dẻo mềm</t>
+    <t>Sét pha, xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">00h25
@@ -119,7 +122,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">00h40
@@ -129,7 +132,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>Sét- đổi chỗ kép cát pha, lẫn dăm sạn TT dẻo mềm</t>
+    <t>Sét, đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">00h55
@@ -149,9 +152,6 @@
     <t>6</t>
   </si>
   <si>
-    <t>Sét pha, xám xanh, xám ghi, TT dẻo mềm lẫn hữu cơ, kẹp cát</t>
-  </si>
-  <si>
     <t xml:space="preserve">02h00
 16/03/2026</t>
   </si>
@@ -159,7 +159,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát pha, xám vàng, xám ghi TT dẻo</t>
+    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">03h46
@@ -169,7 +169,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
   </si>
   <si>
     <t xml:space="preserve">08h00
@@ -179,7 +179,7 @@
     <t>9</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">08h33
@@ -1207,24 +1207,24 @@
         <v>4.35</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" s="9">
         <v>-1.45</v>
@@ -1242,24 +1242,24 @@
         <v>9.6</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13" s="13">
         <v>-3.05</v>
@@ -1277,24 +1277,24 @@
         <v>40.8</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F14" s="16">
         <v>-13.25</v>
@@ -1312,24 +1312,24 @@
         <v>20.8</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" s="19">
         <v>-18.45</v>
@@ -1347,21 +1347,21 @@
         <v>17.26</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E16" s="24" t="s">
         <v>44</v>
@@ -1382,7 +1382,7 @@
         <v>13.6</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1417,7 +1417,7 @@
         <v>1.42</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1452,7 +1452,7 @@
         <v>1.42</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1662,7 +1662,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1691,7 +1691,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1720,7 +1720,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1749,7 +1749,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1778,7 +1778,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1891,10 +1891,10 @@
         <v>65</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C11" s="37" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D11" s="37">
         <v>9</v>

--- a/SGC-CKN/Excel/dbd017ad-7cf6-495c-b512-0f1ca449a9e6_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-15_D800_16-03-2026.xlsx
+++ b/SGC-CKN/Excel/dbd017ad-7cf6-495c-b512-0f1ca449a9e6_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-15_D800_16-03-2026.xlsx
@@ -23,7 +23,7 @@
     <t>Hạng mục</t>
   </si>
   <si>
-    <t>Thi công cọc khoan nhồi đại trà_lô đất ký hiệu CT-02</t>
+    <t>Thi công cọc khoan nhồi, tường vây cho các hạng mục_Lô CT-02</t>
   </si>
   <si>
     <t>Tên bộ phận</t>
